--- a/Results and Summary/Summary Table (Classifier Comparisions).xlsx
+++ b/Results and Summary/Summary Table (Classifier Comparisions).xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/83d3d0baac882484/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Afolabi Soetan\Downloads\New folder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{09F96663-179E-455C-BF3B-1AF766EB106C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8206721C-C138-43F7-B21C-977711FCA970}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{D7E8A444-44CA-4EB7-9290-8E8C446BED87}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="51">
   <si>
     <t>Model 1</t>
   </si>
@@ -123,6 +123,72 @@
   </si>
   <si>
     <t>#4 Classifier</t>
+  </si>
+  <si>
+    <t>Naïve Bayes, XGBoost</t>
+  </si>
+  <si>
+    <t>KNN, RF</t>
+  </si>
+  <si>
+    <t>RF</t>
+  </si>
+  <si>
+    <t>For PCA only datasets with no human-readable columns, RF and KNN were statistically the same</t>
+  </si>
+  <si>
+    <t>For full datasets with that include human-readable columns, RF and KNN were statistically the same</t>
+  </si>
+  <si>
+    <t>For PCA only datasets with no human-readable columns, Naïve Bayes is statistically superior to RF for detecting fraud</t>
+  </si>
+  <si>
+    <t>For full datasets that include human-readable columns, Naïve Bayes is statistically superior to RF for detecting fraud</t>
+  </si>
+  <si>
+    <t>For PCA only datasets with no human-readable columns, RF is statistically superior to Logistic Regression for detecting fraud</t>
+  </si>
+  <si>
+    <t>For full datasets that include human-readable columns, RF is statistically superior to Logistic Regression for detecting fraud</t>
+  </si>
+  <si>
+    <t>For PCA only datasets with no human-readable columns, Linear SVC is statistically superior to RF for detecting fraud</t>
+  </si>
+  <si>
+    <t>For full datasets that include human-readable columns, Linear SVC is statistically superior to RF for detecting fraud</t>
+  </si>
+  <si>
+    <t>XGBoost</t>
+  </si>
+  <si>
+    <t>For PCA only datasets with no human-readable columns, XGBoost is statistically superior to RF for detecting fraud</t>
+  </si>
+  <si>
+    <t>For full datasets that include human-readable columns, XGBoost is statistically superior to RF for detecting fraud</t>
+  </si>
+  <si>
+    <t>For PCA only datasets with no human-readable columns, XGBoost is statistically superior to KNN for detecting fraud</t>
+  </si>
+  <si>
+    <t>For full datasets that include human-readable columns, XGBoost is statistically superior to KNN for detecting fraud</t>
+  </si>
+  <si>
+    <t>For PCA only datasets with no human-readable columns, XGBoost and Naïve Bias were statistically the same</t>
+  </si>
+  <si>
+    <t>For full datasets that include human-readable columns, Linear SVC is statistically superior to XGBoost for detecting fraud</t>
+  </si>
+  <si>
+    <t>For full datasets that include human-readable columns, XGBoost and Naïve Bias were statistically the same</t>
+  </si>
+  <si>
+    <t>For full datasets that include human-readable columns, XGBoost is statistically superior to Logistic Regression for detecting fraud</t>
+  </si>
+  <si>
+    <t>For PCA only datasets with no human-readable columns, XGBoost is statistically superior to Logistic Regression for detecting fraud</t>
+  </si>
+  <si>
+    <t>For PCA only datasets with no include human-readable columns, Linear SVC is statistically superior to XGBoost for detecting fraud</t>
   </si>
 </sst>
 </file>
@@ -503,10 +569,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D3E4F61-E76F-49CB-A8A5-3C9056CBDD55}">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="19.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.140625" bestFit="1" customWidth="1"/>
@@ -812,31 +879,445 @@
         <v>24</v>
       </c>
     </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="1">
+        <v>0.78649999999999998</v>
+      </c>
+      <c r="D14" s="1">
+        <v>0.77500000000000002</v>
+      </c>
+      <c r="E14" s="2">
+        <v>5.2100000000000002E-3</v>
+      </c>
+      <c r="F14" t="s">
+        <v>9</v>
+      </c>
+      <c r="G14" t="s">
+        <v>32</v>
+      </c>
+    </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" t="s">
-        <v>27</v>
-      </c>
-      <c r="D15" t="s">
-        <v>28</v>
+        <v>5</v>
+      </c>
+      <c r="C15" s="1">
+        <v>0.78859999999999997</v>
+      </c>
+      <c r="D15" s="1">
+        <v>0.77290000000000003</v>
+      </c>
+      <c r="E15" s="2">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="F15" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B16" t="s">
         <v>6</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="1">
+        <v>0.78649999999999998</v>
+      </c>
+      <c r="D16" s="1">
+        <v>0.82930000000000004</v>
+      </c>
+      <c r="E16" s="2">
+        <v>3.8199999999999998E-8</v>
+      </c>
+      <c r="F16" t="s">
+        <v>9</v>
+      </c>
+      <c r="G16" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="1">
+        <v>0.78859999999999997</v>
+      </c>
+      <c r="D17" s="1">
+        <v>0.82930000000000004</v>
+      </c>
+      <c r="E17" s="2">
+        <v>1.37E-7</v>
+      </c>
+      <c r="F17" t="s">
+        <v>10</v>
+      </c>
+      <c r="G17" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>31</v>
+      </c>
+      <c r="B18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C18" s="1">
+        <v>0.78649999999999998</v>
+      </c>
+      <c r="D18" s="1">
+        <v>0.61439999999999995</v>
+      </c>
+      <c r="E18" s="2">
+        <v>3.7100000000000001E-17</v>
+      </c>
+      <c r="F18" t="s">
+        <v>9</v>
+      </c>
+      <c r="G18" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>31</v>
+      </c>
+      <c r="B19" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" s="1">
+        <v>0.78859999999999997</v>
+      </c>
+      <c r="D19" s="1">
+        <v>0.61990000000000001</v>
+      </c>
+      <c r="E19" s="2">
+        <v>4.1700000000000002E-18</v>
+      </c>
+      <c r="F19" t="s">
+        <v>10</v>
+      </c>
+      <c r="G19" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>31</v>
+      </c>
+      <c r="B20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" s="1">
+        <v>0.78649999999999998</v>
+      </c>
+      <c r="D20" s="1">
+        <v>0.90300000000000002</v>
+      </c>
+      <c r="E20" s="2">
+        <v>1.5E-16</v>
+      </c>
+      <c r="F20" t="s">
+        <v>9</v>
+      </c>
+      <c r="G20" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" s="1">
+        <v>0.78859999999999997</v>
+      </c>
+      <c r="D21" s="1">
+        <v>0.90439999999999998</v>
+      </c>
+      <c r="E21" s="2">
+        <v>1.5499999999999999E-15</v>
+      </c>
+      <c r="F21" t="s">
+        <v>10</v>
+      </c>
+      <c r="G21" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" s="1">
+        <v>0.78649999999999998</v>
+      </c>
+      <c r="D22" s="1">
+        <v>0.81840000000000002</v>
+      </c>
+      <c r="E22" s="2">
+        <v>1.84E-5</v>
+      </c>
+      <c r="F22" t="s">
+        <v>9</v>
+      </c>
+      <c r="G22" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>31</v>
+      </c>
+      <c r="B23" t="s">
+        <v>40</v>
+      </c>
+      <c r="C23" s="1">
+        <v>0.78859999999999997</v>
+      </c>
+      <c r="D23" s="1">
+        <v>0.82250000000000001</v>
+      </c>
+      <c r="E23" s="2">
+        <v>7.4900000000000003E-6</v>
+      </c>
+      <c r="F23" t="s">
+        <v>10</v>
+      </c>
+      <c r="G23" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" t="s">
         <v>5</v>
       </c>
-      <c r="D16" t="s">
+      <c r="C24" s="1">
+        <v>0.81840000000000002</v>
+      </c>
+      <c r="D24" s="1">
+        <v>0.77500000000000002</v>
+      </c>
+      <c r="E24" s="2">
+        <v>1.1300000000000001E-7</v>
+      </c>
+      <c r="F24" t="s">
+        <v>9</v>
+      </c>
+      <c r="G24" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" t="s">
+        <v>5</v>
+      </c>
+      <c r="C25" s="1">
+        <v>0.82250000000000001</v>
+      </c>
+      <c r="D25" s="1">
+        <v>0.77290000000000003</v>
+      </c>
+      <c r="E25" s="2">
+        <v>4.1499999999999999E-9</v>
+      </c>
+      <c r="F25" t="s">
+        <v>10</v>
+      </c>
+      <c r="G25" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>40</v>
+      </c>
+      <c r="B26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" s="1">
+        <v>0.81840000000000002</v>
+      </c>
+      <c r="D26" s="1">
+        <v>0.82930000000000004</v>
+      </c>
+      <c r="E26" s="2">
+        <v>8.4900000000000003E-2</v>
+      </c>
+      <c r="F26" t="s">
+        <v>9</v>
+      </c>
+      <c r="G26" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="1">
+        <v>0.82250000000000001</v>
+      </c>
+      <c r="D27" s="1">
+        <v>0.82930000000000004</v>
+      </c>
+      <c r="E27" s="2">
+        <v>0.22500000000000001</v>
+      </c>
+      <c r="F27" t="s">
+        <v>10</v>
+      </c>
+      <c r="G27" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" s="1">
+        <v>0.81840000000000002</v>
+      </c>
+      <c r="D28" s="1">
+        <v>0.90300000000000002</v>
+      </c>
+      <c r="E28" s="2">
+        <v>2.3999999999999999E-14</v>
+      </c>
+      <c r="F28" t="s">
+        <v>9</v>
+      </c>
+      <c r="G28" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" s="1">
+        <v>0.82250000000000001</v>
+      </c>
+      <c r="D29" s="1">
+        <v>0.90439999999999998</v>
+      </c>
+      <c r="E29" s="2">
+        <v>5.8500000000000003E-14</v>
+      </c>
+      <c r="F29" t="s">
+        <v>10</v>
+      </c>
+      <c r="G29" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" t="s">
+        <v>13</v>
+      </c>
+      <c r="C30" s="1">
+        <v>0.81840000000000002</v>
+      </c>
+      <c r="D30" s="1">
+        <v>0.61439999999999995</v>
+      </c>
+      <c r="E30" s="2">
+        <v>1.83E-17</v>
+      </c>
+      <c r="F30" t="s">
+        <v>9</v>
+      </c>
+      <c r="G30" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" t="s">
+        <v>13</v>
+      </c>
+      <c r="C31" s="1">
+        <v>0.82850000000000001</v>
+      </c>
+      <c r="D31" s="1">
+        <v>0.61990000000000001</v>
+      </c>
+      <c r="E31" s="2">
+        <v>2.0300000000000001E-17</v>
+      </c>
+      <c r="F31" t="s">
+        <v>10</v>
+      </c>
+      <c r="G31" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>25</v>
+      </c>
+      <c r="B33" t="s">
+        <v>26</v>
+      </c>
+      <c r="C33" t="s">
+        <v>27</v>
+      </c>
+      <c r="D33" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>16</v>
+      </c>
+      <c r="B34" t="s">
+        <v>29</v>
+      </c>
+      <c r="C34" t="s">
+        <v>30</v>
+      </c>
+      <c r="D34" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1042,14 +1523,14 @@
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A854150-EF0E-4280-B26A-E2D190319887}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="09d467f3-b700-42ea-8d14-5b9cd132b1f3"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="09d467f3-b700-42ea-8d14-5b9cd132b1f3"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
